--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2025/Airline_Cumulative_Statistics_2025.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2025/Airline_Cumulative_Statistics_2025.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37" uniqueCount="37">
   <si>
     <t>Row</t>
   </si>
@@ -25,6 +25,9 @@
   </si>
   <si>
     <t>American</t>
+  </si>
+  <si>
+    <t>Avelo</t>
   </si>
   <si>
     <t>Breeze</t>
@@ -166,7 +169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -189,40 +192,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
@@ -353,40 +356,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>5484574707</v>
+        <v>2224603466</v>
       </c>
       <c r="C5" s="0">
-        <v>7129604553</v>
+        <v>3014559871</v>
       </c>
       <c r="D5" s="0">
-        <v>400090</v>
+        <v>508357</v>
       </c>
       <c r="E5" s="0">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="F5" s="0">
-        <v>61579</v>
+        <v>21847</v>
       </c>
       <c r="G5" s="0">
-        <v>3.46</v>
+        <v>3.6800000000000002</v>
       </c>
       <c r="H5" s="0">
-        <v>8.4800000000000004</v>
+        <v>8.5199999999999996</v>
       </c>
       <c r="I5" s="0">
-        <v>76.930000000000007</v>
+        <v>73.799999999999997</v>
       </c>
       <c r="J5" s="0">
-        <v>857</v>
+        <v>808</v>
       </c>
       <c r="K5" s="0">
-        <v>4259.4700000000003</v>
+        <v>4850.75</v>
       </c>
       <c r="L5" s="0">
-        <v>31.530000000000001</v>
+        <v>28.539999999999999</v>
       </c>
       <c r="M5" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="6">
@@ -394,40 +397,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>233986395369</v>
+        <v>5484574707</v>
       </c>
       <c r="C6" s="0">
-        <v>278381772629</v>
+        <v>7129604553</v>
       </c>
       <c r="D6" s="0">
-        <v>787012</v>
+        <v>400090</v>
       </c>
       <c r="E6" s="0">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="F6" s="0">
-        <v>1172551</v>
+        <v>61579</v>
       </c>
       <c r="G6" s="0">
-        <v>3.3100000000000001</v>
+        <v>3.46</v>
       </c>
       <c r="H6" s="0">
-        <v>10.210000000000001</v>
+        <v>8.4800000000000004</v>
       </c>
       <c r="I6" s="0">
-        <v>84.049999999999997</v>
+        <v>76.930000000000007</v>
       </c>
       <c r="J6" s="0">
-        <v>1212</v>
+        <v>857</v>
       </c>
       <c r="K6" s="0">
-        <v>6382.29</v>
+        <v>4259.4700000000003</v>
       </c>
       <c r="L6" s="0">
-        <v>33.659999999999997</v>
+        <v>31.530000000000001</v>
       </c>
       <c r="M6" s="0">
-        <v>0.083000000000000004</v>
+        <v>0.089999999999999997</v>
       </c>
     </row>
     <row r="7">
@@ -435,40 +438,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>31153012118</v>
+        <v>233986395369</v>
       </c>
       <c r="C7" s="0">
-        <v>39706835428</v>
+        <v>278381772629</v>
       </c>
       <c r="D7" s="0">
-        <v>667005</v>
+        <v>787012</v>
       </c>
       <c r="E7" s="0">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="F7" s="0">
-        <v>205620</v>
+        <v>1172551</v>
       </c>
       <c r="G7" s="0">
-        <v>3.4500000000000002</v>
+        <v>3.3100000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>9.0899999999999999</v>
+        <v>10.210000000000001</v>
       </c>
       <c r="I7" s="0">
-        <v>78.459999999999994</v>
+        <v>84.049999999999997</v>
       </c>
       <c r="J7" s="0">
-        <v>918</v>
+        <v>1212</v>
       </c>
       <c r="K7" s="0">
-        <v>5002.0100000000002</v>
+        <v>6382.29</v>
       </c>
       <c r="L7" s="0">
-        <v>23.82</v>
+        <v>33.659999999999997</v>
       </c>
       <c r="M7" s="0">
-        <v>0.068000000000000005</v>
+        <v>0.083000000000000004</v>
       </c>
     </row>
     <row r="8">
@@ -476,40 +479,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>19301382543</v>
+        <v>31153012118</v>
       </c>
       <c r="C8" s="0">
-        <v>23203025381</v>
+        <v>39706835428</v>
       </c>
       <c r="D8" s="0">
-        <v>950554</v>
+        <v>667005</v>
       </c>
       <c r="E8" s="0">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="F8" s="0">
-        <v>84085</v>
+        <v>205620</v>
       </c>
       <c r="G8" s="0">
-        <v>3.4399999999999999</v>
+        <v>3.4500000000000002</v>
       </c>
       <c r="H8" s="0">
-        <v>9.5999999999999996</v>
+        <v>9.0899999999999999</v>
       </c>
       <c r="I8" s="0">
-        <v>83.180000000000007</v>
+        <v>78.459999999999994</v>
       </c>
       <c r="J8" s="0">
-        <v>1159</v>
+        <v>918</v>
       </c>
       <c r="K8" s="0">
-        <v>7973.0600000000004</v>
+        <v>5002.0100000000002</v>
       </c>
       <c r="L8" s="0">
-        <v>35.25</v>
+        <v>23.82</v>
       </c>
       <c r="M8" s="0">
-        <v>0.081000000000000003</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="9">
@@ -517,40 +520,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>53559619102</v>
+        <v>19301382543</v>
       </c>
       <c r="C9" s="0">
-        <v>65021176247</v>
+        <v>23203025381</v>
       </c>
       <c r="D9" s="0">
-        <v>618190</v>
+        <v>950554</v>
       </c>
       <c r="E9" s="0">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="F9" s="0">
-        <v>310105</v>
+        <v>84085</v>
       </c>
       <c r="G9" s="0">
-        <v>2.9500000000000002</v>
+        <v>3.4399999999999999</v>
       </c>
       <c r="H9" s="0">
-        <v>9.8599999999999994</v>
+        <v>9.5999999999999996</v>
       </c>
       <c r="I9" s="0">
-        <v>82.370000000000005</v>
+        <v>83.180000000000007</v>
       </c>
       <c r="J9" s="0">
-        <v>1297</v>
+        <v>1159</v>
       </c>
       <c r="K9" s="0">
-        <v>5577.1999999999998</v>
+        <v>7973.0600000000004</v>
       </c>
       <c r="L9" s="0">
-        <v>34.700000000000003</v>
+        <v>35.25</v>
       </c>
       <c r="M9" s="0">
-        <v>0.088999999999999996</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="10">
@@ -558,40 +561,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>139458641208</v>
+        <v>53559619102</v>
       </c>
       <c r="C10" s="0">
-        <v>180064926062</v>
+        <v>65021176247</v>
       </c>
       <c r="D10" s="0">
-        <v>613175</v>
+        <v>618190</v>
       </c>
       <c r="E10" s="0">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F10" s="0">
-        <v>1415926</v>
+        <v>310105</v>
       </c>
       <c r="G10" s="0">
-        <v>4.8200000000000003</v>
+        <v>2.9500000000000002</v>
       </c>
       <c r="H10" s="0">
-        <v>10.300000000000001</v>
+        <v>9.8599999999999994</v>
       </c>
       <c r="I10" s="0">
-        <v>77.450000000000003</v>
+        <v>82.370000000000005</v>
       </c>
       <c r="J10" s="0">
-        <v>780</v>
+        <v>1297</v>
       </c>
       <c r="K10" s="0">
-        <v>4760.8699999999999</v>
+        <v>5577.1999999999998</v>
       </c>
       <c r="L10" s="0">
-        <v>29.300000000000001</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="M10" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.088999999999999996</v>
       </c>
     </row>
     <row r="11">
@@ -599,40 +602,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>31323133561</v>
+        <v>139458641208</v>
       </c>
       <c r="C11" s="0">
-        <v>39944295863</v>
+        <v>180064926062</v>
       </c>
       <c r="D11" s="0">
-        <v>547782</v>
+        <v>613175</v>
       </c>
       <c r="E11" s="0">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="F11" s="0">
-        <v>215836</v>
+        <v>1415926</v>
       </c>
       <c r="G11" s="0">
-        <v>2.96</v>
+        <v>4.8200000000000003</v>
       </c>
       <c r="H11" s="0">
-        <v>7.6699999999999999</v>
+        <v>10.300000000000001</v>
       </c>
       <c r="I11" s="0">
-        <v>78.420000000000002</v>
+        <v>77.450000000000003</v>
       </c>
       <c r="J11" s="0">
-        <v>957</v>
+        <v>780</v>
       </c>
       <c r="K11" s="0">
-        <v>5113.3999999999996</v>
+        <v>4760.8699999999999</v>
       </c>
       <c r="L11" s="0">
-        <v>26.460000000000001</v>
+        <v>29.300000000000001</v>
       </c>
       <c r="M11" s="0">
-        <v>0.071999999999999995</v>
+        <v>0.080000000000000002</v>
       </c>
     </row>
     <row r="12">
@@ -640,40 +643,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>6052836622</v>
+        <v>31323133561</v>
       </c>
       <c r="C12" s="0">
-        <v>7799993854</v>
+        <v>39944295863</v>
       </c>
       <c r="D12" s="0">
-        <v>352462</v>
+        <v>547782</v>
       </c>
       <c r="E12" s="0">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F12" s="0">
-        <v>37398</v>
+        <v>215836</v>
       </c>
       <c r="G12" s="0">
-        <v>1.6899999999999999</v>
+        <v>2.96</v>
       </c>
       <c r="H12" s="0">
-        <v>5.04</v>
+        <v>7.6699999999999999</v>
       </c>
       <c r="I12" s="0">
-        <v>77.599999999999994</v>
+        <v>78.420000000000002</v>
       </c>
       <c r="J12" s="0">
-        <v>1130</v>
+        <v>957</v>
       </c>
       <c r="K12" s="0">
-        <v>5625.6400000000003</v>
+        <v>5113.3999999999996</v>
       </c>
       <c r="L12" s="0">
-        <v>30.460000000000001</v>
+        <v>26.460000000000001</v>
       </c>
       <c r="M12" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.071999999999999995</v>
       </c>
     </row>
     <row r="13">
@@ -681,40 +684,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>254371378828</v>
+        <v>6052836622</v>
       </c>
       <c r="C13" s="0">
-        <v>309449760908</v>
+        <v>7799993854</v>
       </c>
       <c r="D13" s="0">
-        <v>835402</v>
+        <v>352462</v>
       </c>
       <c r="E13" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F13" s="0">
-        <v>1013537</v>
+        <v>37398</v>
       </c>
       <c r="G13" s="0">
-        <v>2.7400000000000002</v>
+        <v>1.6899999999999999</v>
       </c>
       <c r="H13" s="0">
-        <v>10.18</v>
+        <v>5.04</v>
       </c>
       <c r="I13" s="0">
-        <v>82.200000000000003</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="J13" s="0">
-        <v>1510</v>
+        <v>1130</v>
       </c>
       <c r="K13" s="0">
-        <v>6739.4399999999996</v>
+        <v>5625.6400000000003</v>
       </c>
       <c r="L13" s="0">
-        <v>34.460000000000001</v>
+        <v>30.460000000000001</v>
       </c>
       <c r="M13" s="0">
-        <v>0.082000000000000003</v>
+        <v>0.080000000000000002</v>
       </c>
     </row>
     <row r="14">
@@ -722,40 +725,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>1333844725</v>
+        <v>254371378828</v>
       </c>
       <c r="C14" s="0">
-        <v>1583426825</v>
+        <v>309449760908</v>
       </c>
       <c r="D14" s="0">
-        <v>73579</v>
+        <v>835402</v>
       </c>
       <c r="E14" s="0">
-        <v>50</v>
+        <v>177</v>
       </c>
       <c r="F14" s="0">
-        <v>84613</v>
+        <v>1013537</v>
       </c>
       <c r="G14" s="0">
-        <v>3.9300000000000002</v>
+        <v>2.7400000000000002</v>
       </c>
       <c r="H14" s="0">
-        <v>6.04</v>
+        <v>10.18</v>
       </c>
       <c r="I14" s="0">
-        <v>84.239999999999995</v>
+        <v>82.200000000000003</v>
       </c>
       <c r="J14" s="0">
-        <v>373</v>
+        <v>1510</v>
       </c>
       <c r="K14" s="0">
-        <v>1647.9400000000001</v>
+        <v>6739.4399999999996</v>
       </c>
       <c r="L14" s="0">
-        <v>32.880000000000003</v>
+        <v>34.460000000000001</v>
       </c>
       <c r="M14" s="0">
-        <v>0.13500000000000001</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="15">
@@ -763,40 +766,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>6678329212</v>
+        <v>1333844725</v>
       </c>
       <c r="C15" s="0">
-        <v>8382640866</v>
+        <v>1583426825</v>
       </c>
       <c r="D15" s="0">
-        <v>185088</v>
+        <v>73579</v>
       </c>
       <c r="E15" s="0">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="F15" s="0">
-        <v>250544</v>
+        <v>84613</v>
       </c>
       <c r="G15" s="0">
-        <v>5.5300000000000002</v>
+        <v>3.9300000000000002</v>
       </c>
       <c r="H15" s="0">
-        <v>9.3800000000000008</v>
+        <v>6.04</v>
       </c>
       <c r="I15" s="0">
-        <v>79.670000000000002</v>
+        <v>84.239999999999995</v>
       </c>
       <c r="J15" s="0">
-        <v>449</v>
+        <v>373</v>
       </c>
       <c r="K15" s="0">
-        <v>1723.9300000000001</v>
+        <v>1647.9400000000001</v>
       </c>
       <c r="L15" s="0">
-        <v>23.140000000000001</v>
+        <v>32.880000000000003</v>
       </c>
       <c r="M15" s="0">
-        <v>0.086999999999999994</v>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -804,40 +807,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>10187243794</v>
+        <v>6678329212</v>
       </c>
       <c r="C16" s="0">
-        <v>12416284803</v>
+        <v>8382640866</v>
       </c>
       <c r="D16" s="0">
-        <v>66490</v>
+        <v>185088</v>
       </c>
       <c r="E16" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F16" s="0">
-        <v>322932</v>
+        <v>250544</v>
       </c>
       <c r="G16" s="0">
-        <v>1.73</v>
+        <v>5.5300000000000002</v>
       </c>
       <c r="H16" s="0">
-        <v>3.1200000000000001</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="I16" s="0">
-        <v>82.049999999999997</v>
+        <v>79.670000000000002</v>
       </c>
       <c r="J16" s="0">
-        <v>521</v>
+        <v>449</v>
       </c>
       <c r="K16" s="0">
-        <v>1950.49</v>
+        <v>1723.9300000000001</v>
       </c>
       <c r="L16" s="0">
-        <v>26.57</v>
+        <v>23.140000000000001</v>
       </c>
       <c r="M16" s="0">
-        <v>0.091999999999999998</v>
+        <v>0.086999999999999994</v>
       </c>
     </row>
     <row r="17">
@@ -845,40 +848,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>1186997580</v>
+        <v>10187243794</v>
       </c>
       <c r="C17" s="0">
-        <v>1410434550</v>
+        <v>12416284803</v>
       </c>
       <c r="D17" s="0">
-        <v>66940</v>
+        <v>66490</v>
       </c>
       <c r="E17" s="0">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="F17" s="0">
-        <v>75533</v>
+        <v>322932</v>
       </c>
       <c r="G17" s="0">
-        <v>3.5800000000000001</v>
+        <v>1.73</v>
       </c>
       <c r="H17" s="0">
-        <v>5.9000000000000004</v>
+        <v>3.1200000000000001</v>
       </c>
       <c r="I17" s="0">
-        <v>84.159999999999997</v>
+        <v>82.049999999999997</v>
       </c>
       <c r="J17" s="0">
-        <v>373</v>
+        <v>521</v>
       </c>
       <c r="K17" s="0">
-        <v>2146.02</v>
+        <v>1950.49</v>
       </c>
       <c r="L17" s="0">
-        <v>42.920000000000002</v>
+        <v>26.57</v>
       </c>
       <c r="M17" s="0">
-        <v>0.189</v>
+        <v>0.091999999999999998</v>
       </c>
     </row>
     <row r="18">
@@ -886,40 +889,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>2957441017</v>
+        <v>1186997580</v>
       </c>
       <c r="C18" s="0">
-        <v>3583820052</v>
+        <v>1410434550</v>
       </c>
       <c r="D18" s="0">
-        <v>214857</v>
+        <v>66940</v>
       </c>
       <c r="E18" s="0">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="F18" s="0">
-        <v>101988</v>
+        <v>75533</v>
       </c>
       <c r="G18" s="0">
-        <v>6.1100000000000003</v>
+        <v>3.5800000000000001</v>
       </c>
       <c r="H18" s="0">
-        <v>9.6400000000000006</v>
+        <v>5.9000000000000004</v>
       </c>
       <c r="I18" s="0">
-        <v>82.519999999999996</v>
+        <v>84.159999999999997</v>
       </c>
       <c r="J18" s="0">
-        <v>462</v>
+        <v>373</v>
       </c>
       <c r="K18" s="0">
-        <v>1879.78</v>
+        <v>2146.02</v>
       </c>
       <c r="L18" s="0">
-        <v>24.73</v>
+        <v>42.920000000000002</v>
       </c>
       <c r="M18" s="0">
-        <v>0.084000000000000005</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="19">
@@ -927,40 +930,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>3190002264</v>
+        <v>2957441017</v>
       </c>
       <c r="C19" s="0">
-        <v>3887577792</v>
+        <v>3583820052</v>
       </c>
       <c r="D19" s="0">
-        <v>238209</v>
+        <v>214857</v>
       </c>
       <c r="E19" s="0">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F19" s="0">
-        <v>84542</v>
+        <v>101988</v>
       </c>
       <c r="G19" s="0">
-        <v>5.1799999999999997</v>
+        <v>6.1100000000000003</v>
       </c>
       <c r="H19" s="0">
-        <v>10.32</v>
+        <v>9.6400000000000006</v>
       </c>
       <c r="I19" s="0">
-        <v>82.060000000000002</v>
+        <v>82.519999999999996</v>
       </c>
       <c r="J19" s="0">
-        <v>619</v>
+        <v>462</v>
       </c>
       <c r="K19" s="0">
-        <v>1264.46</v>
+        <v>1879.78</v>
       </c>
       <c r="L19" s="0">
-        <v>17.02</v>
+        <v>24.73</v>
       </c>
       <c r="M19" s="0">
-        <v>0.055</v>
+        <v>0.084000000000000005</v>
       </c>
     </row>
     <row r="20">
@@ -968,40 +971,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>1792509186</v>
+        <v>3190002264</v>
       </c>
       <c r="C20" s="0">
-        <v>2126496854</v>
+        <v>3887577792</v>
       </c>
       <c r="D20" s="0">
-        <v>83523</v>
+        <v>238209</v>
       </c>
       <c r="E20" s="0">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="F20" s="0">
-        <v>148898</v>
+        <v>84542</v>
       </c>
       <c r="G20" s="0">
-        <v>5.8499999999999996</v>
+        <v>5.1799999999999997</v>
       </c>
       <c r="H20" s="0">
-        <v>8.4299999999999997</v>
+        <v>10.32</v>
       </c>
       <c r="I20" s="0">
-        <v>84.290000000000006</v>
+        <v>82.060000000000002</v>
       </c>
       <c r="J20" s="0">
-        <v>286</v>
+        <v>619</v>
       </c>
       <c r="K20" s="0">
-        <v>1955.23</v>
+        <v>1263.77</v>
       </c>
       <c r="L20" s="0">
-        <v>39.100000000000001</v>
+        <v>17.02</v>
       </c>
       <c r="M20" s="0">
-        <v>0.19700000000000001</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="21">
@@ -1009,40 +1012,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>6667124439</v>
+        <v>1792509186</v>
       </c>
       <c r="C21" s="0">
-        <v>8301200126</v>
+        <v>2126496854</v>
       </c>
       <c r="D21" s="0">
-        <v>90992</v>
+        <v>83523</v>
       </c>
       <c r="E21" s="0">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="F21" s="0">
-        <v>244872</v>
+        <v>148898</v>
       </c>
       <c r="G21" s="0">
-        <v>2.6800000000000002</v>
+        <v>5.8499999999999996</v>
       </c>
       <c r="H21" s="0">
-        <v>4.7400000000000002</v>
+        <v>8.4299999999999997</v>
       </c>
       <c r="I21" s="0">
-        <v>80.319999999999993</v>
+        <v>84.290000000000006</v>
       </c>
       <c r="J21" s="0">
-        <v>471</v>
+        <v>286</v>
       </c>
       <c r="K21" s="0">
-        <v>2849.4200000000001</v>
+        <v>1955.23</v>
       </c>
       <c r="L21" s="0">
-        <v>39.640000000000001</v>
+        <v>39.100000000000001</v>
       </c>
       <c r="M21" s="0">
-        <v>0.14799999999999999</v>
+        <v>0.19700000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1050,40 +1053,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>10475360625</v>
+        <v>6667124439</v>
       </c>
       <c r="C22" s="0">
-        <v>13371225732</v>
+        <v>8301200126</v>
       </c>
       <c r="D22" s="0">
-        <v>153781</v>
+        <v>90992</v>
       </c>
       <c r="E22" s="0">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F22" s="0">
-        <v>363631</v>
+        <v>244872</v>
       </c>
       <c r="G22" s="0">
-        <v>4.1799999999999997</v>
+        <v>2.6800000000000002</v>
       </c>
       <c r="H22" s="0">
-        <v>7.8499999999999996</v>
+        <v>4.7400000000000002</v>
       </c>
       <c r="I22" s="0">
-        <v>78.340000000000003</v>
+        <v>80.319999999999993</v>
       </c>
       <c r="J22" s="0">
-        <v>491</v>
+        <v>471</v>
       </c>
       <c r="K22" s="0">
-        <v>1523.4000000000001</v>
+        <v>2849.4200000000001</v>
       </c>
       <c r="L22" s="0">
-        <v>20.32</v>
+        <v>39.640000000000001</v>
       </c>
       <c r="M22" s="0">
-        <v>0.078</v>
+        <v>0.14799999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1091,40 +1094,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>21877001195</v>
+        <v>10475360625</v>
       </c>
       <c r="C23" s="0">
-        <v>27557473645</v>
+        <v>13371225732</v>
       </c>
       <c r="D23" s="0">
-        <v>129670</v>
+        <v>153781</v>
       </c>
       <c r="E23" s="0">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F23" s="0">
-        <v>869483</v>
+        <v>363631</v>
       </c>
       <c r="G23" s="0">
-        <v>4.0899999999999999</v>
+        <v>4.1799999999999997</v>
       </c>
       <c r="H23" s="0">
-        <v>7.04</v>
+        <v>7.8499999999999996</v>
       </c>
       <c r="I23" s="0">
-        <v>79.390000000000001</v>
+        <v>78.340000000000003</v>
       </c>
       <c r="J23" s="0">
-        <v>459</v>
+        <v>491</v>
       </c>
       <c r="K23" s="0">
-        <v>1626.5799999999999</v>
+        <v>1523.4000000000001</v>
       </c>
       <c r="L23" s="0">
-        <v>23.82</v>
+        <v>20.32</v>
       </c>
       <c r="M23" s="0">
-        <v>0.087999999999999995</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="24">
@@ -1132,39 +1135,80 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>1131445254792</v>
+        <v>21877001195</v>
       </c>
       <c r="C24" s="0">
-        <v>1380192482862</v>
+        <v>27557473645</v>
       </c>
       <c r="D24" s="0">
-        <v>543655</v>
+        <v>129670</v>
       </c>
       <c r="E24" s="0">
+        <v>68</v>
+      </c>
+      <c r="F24" s="0">
+        <v>869483</v>
+      </c>
+      <c r="G24" s="0">
+        <v>4.0899999999999999</v>
+      </c>
+      <c r="H24" s="0">
+        <v>7.04</v>
+      </c>
+      <c r="I24" s="0">
+        <v>79.390000000000001</v>
+      </c>
+      <c r="J24" s="0">
+        <v>459</v>
+      </c>
+      <c r="K24" s="0">
+        <v>1626.5799999999999</v>
+      </c>
+      <c r="L24" s="0">
+        <v>23.82</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.087999999999999995</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>1133669858258</v>
+      </c>
+      <c r="C25" s="0">
+        <v>1383207042733</v>
+      </c>
+      <c r="D25" s="0">
+        <v>543572</v>
+      </c>
+      <c r="E25" s="0">
         <v>141</v>
       </c>
-      <c r="F24" s="0">
-        <v>8622704</v>
-      </c>
-      <c r="G24" s="0">
+      <c r="F25" s="0">
+        <v>8644551</v>
+      </c>
+      <c r="G25" s="0">
         <v>3.3999999999999999</v>
       </c>
-      <c r="H24" s="0">
+      <c r="H25" s="0">
         <v>8.7799999999999994</v>
       </c>
-      <c r="I24" s="0">
-        <v>81.980000000000004</v>
-      </c>
-      <c r="J24" s="0">
+      <c r="I25" s="0">
+        <v>81.959999999999994</v>
+      </c>
+      <c r="J25" s="0">
         <v>938</v>
       </c>
-      <c r="K24" s="0">
-        <v>5235.6700000000001</v>
-      </c>
-      <c r="L24" s="0">
-        <v>32.57</v>
-      </c>
-      <c r="M24" s="0">
+      <c r="K25" s="0">
+        <v>5234.79</v>
+      </c>
+      <c r="L25" s="0">
+        <v>32.560000000000002</v>
+      </c>
+      <c r="M25" s="0">
         <v>0.085000000000000006</v>
       </c>
     </row>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2025/Airline_Cumulative_Statistics_2025.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2025/Airline_Cumulative_Statistics_2025.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="41" uniqueCount="41">
   <si>
     <t>Row</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -169,7 +181,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -192,40 +204,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
@@ -1176,39 +1188,203 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
+        <v>710722755743</v>
+      </c>
+      <c r="C25" s="0">
+        <v>852596667472</v>
+      </c>
+      <c r="D25" s="0">
+        <v>784798</v>
+      </c>
+      <c r="E25" s="0">
+        <v>174</v>
+      </c>
+      <c r="F25" s="0">
+        <v>3361325</v>
+      </c>
+      <c r="G25" s="0">
+        <v>3.0899999999999999</v>
+      </c>
+      <c r="H25" s="0">
+        <v>10.109999999999999</v>
+      </c>
+      <c r="I25" s="0">
+        <v>83.359999999999999</v>
+      </c>
+      <c r="J25" s="0">
+        <v>1292</v>
+      </c>
+      <c r="K25" s="0">
+        <v>6710.0200000000004</v>
+      </c>
+      <c r="L25" s="0">
+        <v>35.259999999999998</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.085999999999999993</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>270211365554</v>
+      </c>
+      <c r="C26" s="0">
+        <v>338584070058</v>
+      </c>
+      <c r="D26" s="0">
+        <v>640736</v>
+      </c>
+      <c r="E26" s="0">
+        <v>161</v>
+      </c>
+      <c r="F26" s="0">
+        <v>2136147</v>
+      </c>
+      <c r="G26" s="0">
+        <v>4.04</v>
+      </c>
+      <c r="H26" s="0">
+        <v>10.17</v>
+      </c>
+      <c r="I26" s="0">
+        <v>79.810000000000002</v>
+      </c>
+      <c r="J26" s="0">
+        <v>948</v>
+      </c>
+      <c r="K26" s="0">
+        <v>5052.71</v>
+      </c>
+      <c r="L26" s="0">
+        <v>30.489999999999998</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.080000000000000002</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>86389882924</v>
+      </c>
+      <c r="C27" s="0">
+        <v>109405723958</v>
+      </c>
+      <c r="D27" s="0">
+        <v>530941</v>
+      </c>
+      <c r="E27" s="0">
+        <v>193</v>
+      </c>
+      <c r="F27" s="0">
+        <v>600043</v>
+      </c>
+      <c r="G27" s="0">
+        <v>2.9100000000000001</v>
+      </c>
+      <c r="H27" s="0">
+        <v>7.5300000000000002</v>
+      </c>
+      <c r="I27" s="0">
+        <v>78.959999999999994</v>
+      </c>
+      <c r="J27" s="0">
+        <v>940</v>
+      </c>
+      <c r="K27" s="0">
+        <v>5167.5</v>
+      </c>
+      <c r="L27" s="0">
+        <v>26.609999999999999</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.072999999999999995</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>66345854037</v>
+      </c>
+      <c r="C28" s="0">
+        <v>82620581245</v>
+      </c>
+      <c r="D28" s="0">
+        <v>114152</v>
+      </c>
+      <c r="E28" s="0">
+        <v>69</v>
+      </c>
+      <c r="F28" s="0">
+        <v>2547036</v>
+      </c>
+      <c r="G28" s="0">
+        <v>3.52</v>
+      </c>
+      <c r="H28" s="0">
+        <v>6.0999999999999996</v>
+      </c>
+      <c r="I28" s="0">
+        <v>80.299999999999997</v>
+      </c>
+      <c r="J28" s="0">
+        <v>461</v>
+      </c>
+      <c r="K28" s="0">
+        <v>1809.03</v>
+      </c>
+      <c r="L28" s="0">
+        <v>26.02</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.097000000000000003</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
         <v>1133669858258</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C29" s="0">
         <v>1383207042733</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D29" s="0">
         <v>543572</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E29" s="0">
         <v>141</v>
       </c>
-      <c r="F25" s="0">
+      <c r="F29" s="0">
         <v>8644551</v>
       </c>
-      <c r="G25" s="0">
+      <c r="G29" s="0">
         <v>3.3999999999999999</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H29" s="0">
         <v>8.7799999999999994</v>
       </c>
-      <c r="I25" s="0">
+      <c r="I29" s="0">
         <v>81.959999999999994</v>
       </c>
-      <c r="J25" s="0">
+      <c r="J29" s="0">
         <v>938</v>
       </c>
-      <c r="K25" s="0">
+      <c r="K29" s="0">
         <v>5234.79</v>
       </c>
-      <c r="L25" s="0">
+      <c r="L29" s="0">
         <v>32.560000000000002</v>
       </c>
-      <c r="M25" s="0">
+      <c r="M29" s="0">
         <v>0.085000000000000006</v>
       </c>
     </row>
